--- a/DayZ - Time Acceleration Values (github).xlsx
+++ b/DayZ - Time Acceleration Values (github).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e78a9aefdc4e9639/Dokumente/DayZ/Day - Documentation COPY/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lutz-\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A13076B4-05C5-4994-8060-E04334CC3F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BEF3319-C71C-4F48-8F15-B573E90A9B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1650" yWindow="-16470" windowWidth="29040" windowHeight="16440" xr2:uid="{A0CE5FB0-3C67-4DDB-B6B6-1453EAD54999}"/>
+    <workbookView xWindow="7500" yWindow="8205" windowWidth="28800" windowHeight="15885" xr2:uid="{A0CE5FB0-3C67-4DDB-B6B6-1453EAD54999}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -206,9 +206,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -246,7 +246,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -352,7 +352,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -494,7 +494,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -503,22 +503,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57652D3B-5E43-4BC9-904E-66B4DF09D026}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.41796875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.26171875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.41796875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="33.578125" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="11.41796875" style="1"/>
+    <col min="1" max="1" width="40.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="33.5703125" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -531,12 +531,12 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="10">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>9</v>
@@ -547,12 +547,12 @@
       </c>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="10">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>10</v>
@@ -563,20 +563,19 @@
       </c>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="5">
-        <f>TimeDaylight+TimeNight</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>5</v>
@@ -584,20 +583,20 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" ht="14.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="8">
         <f>24/TimeDay</f>
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -605,13 +604,13 @@
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
     </row>
-    <row r="9" spans="1:5" ht="14.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B9" s="9">
         <f>TimeDaylight/TimeNight</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>7</v>
@@ -619,21 +618,21 @@
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="4"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="4"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -641,7 +640,6 @@
       <c r="E12" s="3"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="pVwbL2H/DZYD6htzk9JzFeny256kdxsAq7b3WObNLr6wNGVC4r2osmCJ16g/B5BHnk9+AfHuICzCKIkJJYgTZg==" saltValue="HOWKXH4AlP2CDS6KJ32TGQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
